--- a/AAII_Financials/Yearly/ORMP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ORMP_YR_FIN.xlsx
@@ -2576,7 +2576,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>95700</v>
+        <v>93700</v>
       </c>
       <c r="E47" s="3">
         <v>10900</v>
@@ -2846,7 +2846,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
